--- a/data/trans_orig/P80_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P80_R-Estudios-trans_orig.xlsx
@@ -725,17 +725,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29678</t>
+          <t>31721</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>24019</t>
+          <t>26831</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15262</t>
+          <t>18116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35258</t>
+          <t>38645</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>496194</t>
+          <t>557478</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485260</t>
+          <t>546808</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>503308</t>
+          <t>565734</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>748322</t>
+          <t>814161</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>743843</t>
+          <t>809258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>751052</t>
+          <t>817215</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1244516</t>
+          <t>1371640</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1233277</t>
+          <t>1359826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1253273</t>
+          <t>1380355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>753597</t>
+          <t>819942</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>753597</t>
+          <t>819942</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753597</t>
+          <t>819942</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268535</t>
+          <t>1398471</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268535</t>
+          <t>1398471</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268535</t>
+          <t>1398471</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38733</t>
+          <t>48808</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22463</t>
+          <t>32693</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57584</t>
+          <t>68573</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33625</t>
+          <t>39366</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>28205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47980</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>72358</t>
+          <t>88174</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52775</t>
+          <t>67357</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97995</t>
+          <t>114748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2249988</t>
+          <t>2180035</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2231137</t>
+          <t>2160270</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2266258</t>
+          <t>2196150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2200238</t>
+          <t>2127618</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2185883</t>
+          <t>2112638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2211808</t>
+          <t>2138779</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4450225</t>
+          <t>4307653</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4424588</t>
+          <t>4281079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4469808</t>
+          <t>4328470</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288721</t>
+          <t>2228843</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288721</t>
+          <t>2228843</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288721</t>
+          <t>2228843</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2233863</t>
+          <t>2166984</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2233863</t>
+          <t>2166984</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2233863</t>
+          <t>2166984</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4522583</t>
+          <t>4395827</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4522583</t>
+          <t>4395827</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4522583</t>
+          <t>4395827</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>9213</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>9979</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17763</t>
+          <t>16649</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>19192</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28344</t>
+          <t>28159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>637681</t>
+          <t>701255</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628701</t>
+          <t>693469</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>641998</t>
+          <t>705867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>649521</t>
+          <t>724143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>642006</t>
+          <t>717473</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>654022</t>
+          <t>728870</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1287201</t>
+          <t>1425397</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1277042</t>
+          <t>1416430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1293739</t>
+          <t>1432773</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645617</t>
+          <t>710468</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645617</t>
+          <t>710468</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645617</t>
+          <t>710468</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659769</t>
+          <t>734122</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659769</t>
+          <t>734122</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659769</t>
+          <t>734122</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1305386</t>
+          <t>1444589</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1305386</t>
+          <t>1444589</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1305386</t>
+          <t>1444589</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45559</t>
+          <t>59644</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87394</t>
+          <t>105197</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49148</t>
+          <t>55125</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35783</t>
+          <t>43247</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66517</t>
+          <t>73964</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>114562</t>
+          <t>134197</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90937</t>
+          <t>109178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143438</t>
+          <t>164662</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3383862</t>
+          <t>3438768</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3361882</t>
+          <t>3412643</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3403717</t>
+          <t>3458196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3598080</t>
+          <t>3665922</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3580711</t>
+          <t>3647083</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3611445</t>
+          <t>3677800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6981942</t>
+          <t>7104690</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6953066</t>
+          <t>7074225</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7005567</t>
+          <t>7129709</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3449276</t>
+          <t>3517840</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3449276</t>
+          <t>3517840</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3449276</t>
+          <t>3517840</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3647228</t>
+          <t>3721047</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3647228</t>
+          <t>3721047</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3647228</t>
+          <t>3721047</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7096504</t>
+          <t>7238887</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7096504</t>
+          <t>7238887</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7096504</t>
+          <t>7238887</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
